--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0160.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0160.xlsx
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Cậu tưởng cậu chạy đi đâu được hả, nhóc?</t>
+          <t>Mày tưởng mày chạy đi đâu được hả, nhóc?</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Thôi, ít ra sau này tụi này cũng sẽ có xác cậu để mà nhận…</t>
+          <t>Thôi, ít ra sau này tụi này cũng sẽ có xác mày để mà nhận…</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Dù ngươi có giết ta... Sự thật vẫn không thay đổi!</t>
+          <t>Dù mày có giết tao... Sự thật vẫn không thay đổi!</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Cậu nghĩ mình trơn tru lắm à?</t>
+          <t>Mày nghĩ mình trơn tru lắm à?</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Thật tốt quá... Cảm ơn cậu.</t>
+          <t>Thật tốt quá... Cảm ơn mày.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Từ đó đến giờ, tụi mình phải vật lộn để sống sót. Ta đã làm đủ mọi việc lặt vặt để kiếm sống, lo cho em gái ta.</t>
+          <t>Từ đó đến giờ, tụi mình phải vật lộn để sống sót. Tao đã làm đủ mọi việc lặt vặt để kiếm sống, lo cho em gái tao.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>...Đúng vậy. Ta không nên tự quyết định thay cho con bé.</t>
+          <t>...Đúng vậy. Tao không nên tự quyết định thay cho con bé.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Xììì... Grrr... Ngươi làm đau bạn ta... Ngươi chết đây!</t>
+          <t>Xììì... Grrr... Mày làm đau bạn tao... Mày chết đây!</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Trong hoang dã này, cậu chẳng có cơ hội thắng ta đâu. Hãy đầu hàng đi, khi còn có thể.</t>
+          <t>Trong hoang dã này, cậu chẳng có cơ hội thắng tao đâu. Hãy đầu hàng đi, khi còn có thể.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>...Hay là cậu thích bị xé xác thành từng mảnh hơn?</t>
+          <t>...Hay là mày thích bị xé xác thành từng mảnh hơn?</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Một số người trong đó thậm chí là Cộng Hưởng Giả hoặc từng phục vụ trong quân đội!</t>
+          <t>Một số người trong đó thậm chí là Resonator hoặc từng phục vụ trong quân đội!</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Nếu thấy gì khả nghi thì rung chuông báo ta nhé? Gặp lại sau!</t>
+          <t>Nếu thấy gì khả nghi thì rung chuông báo tao nhé? Gặp lại sau!</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Vậy à…? Rồi sau đó cậu làm gì?</t>
+          <t>Vậy à…? Rồi sau đó mày làm gì?</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tên ta là Yinlin. Ta cũng là Tuần Tra viên… Đây, thẻ căn cước của ta.</t>
+          <t>Tên tao là Yinlin. Tao cũng là Tuần Tra viên… Đây, thẻ căn cước của tao.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Cậu chắc đây là thật à? Ta chưa thấy cô ấy bao giờ cả.</t>
+          <t>Cậu chắc đây là thật à? Tao chưa thấy cô ấy bao giờ cả.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Ngươi tưởng ta không nhận ra giấy tờ giả hả? Câm miệng lại đi.</t>
+          <t>Mày tưởng tao không nhận ra giấy tờ giả hả? Câm miệng lại đi.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Ta biết... Ta biết rõ lắm rồi. Không cần anh nhắc đâu. Làm ơn. Để chúng tôi yên.</t>
+          <t>Tao biết... Tao biết rõ lắm rồi. Không cần anh nhắc đâu. Làm ơn. Để chúng tôi yên.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Hehe... Không ngờ cậu lại quan tâm ta đến vậy.</t>
+          <t>Hehe... Không ngờ bạn lại quan tâm tao đến vậy.</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Cậu vào rồi à? Chẳng thèm nghĩ ngợi gì à?</t>
+          <t>Mày vào rồi à? Chẳng thèm nghĩ ngợi gì à?</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Phần còn lại giao cho cậu đấy, Rover.</t>
+          <t>Phần còn lại giao cho cậu đấy, Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Đến lúc để người của ta đưa {Male=hắn;Female=cô ấy} về trại...</t>
+          <t>Đến lúc để người của ta đưa {Male=him;Female=her} về trại...</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Phần còn lại, mình giao cho cậu đây, Rover.</t>
+          <t>Phần còn lại, mình giao cho cậu đây, Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Nhưng đây không phải vấn đề của cậu. Mình đang làm nhiệm vụ. R?i ?i và quên hết những gì xảy ra hôm nay, được chứ?</t>
+          <t>Nhưng đây không phải vấn đề của cậu. Mình đang làm nhiệm vụ. Cút đi và quên hết những gì xảy ra hôm nay, được chứ?</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hừ… Ừ… Khụ… Ta sẽ không… để ngươi đâu! Aaaagh!</t>
+          <t>Hừ… Ừ… Khụ… Tao sẽ không… để mày đâu! Aaaagh!</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Một {Male=gã đàn ông;Female=con đàn bà} như thế thì có khác gì đâu. Loại bỏ ngay đi!</t>
+          <t>Một {Male=man;Female=woman} như thế thì có khác gì đâu. Loại bỏ ngay đi!</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>*thở dài* Giờ tính sau. Ta phải đưa tụi bay đến nơi an toàn trước đã.</t>
+          <t>*thở dài* Giờ tính sau. Tao phải đưa tụi bay đến nơi an toàn trước đã.</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Cái quái... Lũ ngốc đó. Chúng nó đáng ra phải lo cho cậu chứ!</t>
+          <t>Cái quái... Lũ ngốc đó. Chúng nó đáng ra phải lo cho mày chứ!</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Ngươi nghĩ tụi ta ngu lắm hả? Bọn ta sẽ lấy con rối, còn tụi bay thì chuẩn bị đi đời đi!</t>
+          <t>Mày nghĩ tụi tao ngu lắm hả? Bọn tao sẽ lấy con rối, còn tụi bay thì chuẩn bị đi đời đi!</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Tính cả ta. Chứ họ có tha cho ta đâu.</t>
+          <t>Tính cả tao. Chứ họ có tha cho tao đâu.</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Ừ, nhưng cẩn thận vẫn hơn. Ta thấy quá nhiều người chết vì liều lĩnh rồi.</t>
+          <t>Ừ, nhưng cẩn thận vẫn hơn. Tao thấy quá nhiều người chết vì liều lĩnh rồi.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Ôi, thật á? Lần sau để ta ngồi chơi, mọi việc giao hết cho ngươi nhé.</t>
+          <t>Ôi, thật á? Lần sau để tao ngồi chơi, mọi việc giao hết cho mày nhé.</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Giống như ta đã làm với ngươi... Thử cảm nhận lưng ngươi xem.</t>
+          <t>Giống như tao đã làm với mày... Thử cảm nhận lưng mày xem.</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Ngươi gài thiết bị theo dõi lên ta à!?</t>
+          <t>Mày gài thiết bị theo dõi lên tao à!?</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>"Đừng tin ai cả"... Đó là bài học đầu tiên ta học được trong huấn luyện.</t>
+          <t>"Đừng tin ai cả"... Đó là bài học đầu tiên tao học được trong huấn luyện.</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Ừ, ta định làm rồi. Chắc sẽ tìm được vài manh mối.</t>
+          <t>Ừ, tao định làm rồi. Chắc sẽ tìm được vài manh mối.</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Đi thu gom mấy con rối đi. Ta sẽ trông Lirong và Yuanyuan.</t>
+          <t>Đi thu gom mấy con rối đi. Tao sẽ trông Lirong và Yuanyuan.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Chẳng lẽ ta đang ở căn cứ hoạt động của bọn chúng?</t>
+          <t>Chẳng lẽ tao đang ở căn cứ hoạt động của bọn chúng?</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Yinlin… Quả thật là cậu!</t>
+          <t>Yinlin… Quả thật là mày!</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Lúc đó ta đã dùng điện áp tối đa rồi. Không ngờ ngươi tỉnh lại sớm vậy.</t>
+          <t>Lúc đó tao đã dùng điện áp tối đa rồi. Không ngờ mày tỉnh lại sớm vậy.</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Tưởng cậu sẽ không tỉnh lại nữa. Ta định gọi bác sĩ Wu Sheng đến khám cho cậu rồi đấy.</t>
+          <t>Tưởng cậu sẽ không tỉnh lại nữa. Tao định gọi bác sĩ Wu Sheng đến khám cho cậu rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Sao cậu hỗn xược thế hả nhóc con. Nói chuyện với cô Yinlin mà không biết lễ phép à?</t>
+          <t>Sao mày hỗn xược thế hả nhóc con. Nói chuyện với cô Yinlin mà không biết lễ phép à?</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>"Hội Ngộ Gia Đình" đấy. Không đời nào ta để ai rời khỏi trại này.</t>
+          <t>"Hội Ngộ Gia Đình" đấy. Không đời nào tao để ai rời khỏi trại này.</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Ngươi nghĩ ta sẽ tin à?</t>
+          <t>Mày nghĩ tao sẽ tin à?</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Dù sao ngươi cũng định hỏi Thợ Làm Búp Bê về ký ức của mình, sao không đi cùng ta?</t>
+          <t>Dù sao mày cũng định hỏi Thợ Làm Búp Bê về ký ức của mình, sao không đi cùng tao?</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Ta đã đoán trước được điều đó. Nhưng biết đâu sau này ngươi sẽ thay đổi suy nghĩ.</t>
+          <t>Tao đã đoán trước được điều đó. Nhưng biết đâu sau này mày sẽ thay đổi suy nghĩ.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Ta sẽ làm bất cứ điều gì cho Sư phụ Thợ Múa Rối. Dù có làm gì cũng không đủ để đền đáp ơn nghĩa của ngài...</t>
+          <t>Tao sẽ làm bất cứ điều gì cho Sư phụ Thợ Múa Rối. Dù có làm gì cũng không đủ để đền đáp ơn nghĩa của ngài...</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Xin chào, người lạ ơi. Ta là Jinlu. Ta và Anh ấy Chang là lính gác ở đây.</t>
+          <t>Xin chào, người lạ ơi. Ta là Jinlu. Ta và He Chang là lính gác ở đây.</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Cậu là Cộng Hưởng Giả phải không?</t>
+          <t>Cậu là Resonator phải không?</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Đúng vậy. Ta với Lirong và cậu từng là Midnight Rangers đấy.</t>
+          <t>Đúng vậy. Tao với Lirong và cậu từng là Midnight Rangers đấy.</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Cậu phát hiện ra Jinlu đã gặp đồng đội đã hy sinh của mình, Anh ấy Chang, tại đây và quyết định ở lại vì mối quan hệ gắn bó sâu sắc giữa họ.</t>
+          <t>Cậu phát hiện ra Jinlu đã gặp đồng đội đã hy sinh của mình, He Chang, tại đây và quyết định ở lại vì mối quan hệ gắn bó sâu sắc giữa họ.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Ôi... Vậy là cậu đã nhận lời mời của ta rồi, Rover.</t>
+          <t>Ôi... Vậy là cậu đã nhận lời mời của ta rồi, Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Giờ thì, Yuanyuan à, đừng sợ... {Male=Hắn;Female=Cô ấy} không phải là một trong những tên Tuần Tra độc ác đâu. Con an toàn với ta.</t>
+          <t>Giờ thì, Yuanyuan à, đừng sợ... {Male=He;Female=She} không phải là một trong những tên Tuần Tra độc ác đâu. Con an toàn với ta.</t>
         </is>
       </c>
     </row>
